--- a/02_DIA_inicio_2026_analisis_assets/rbd_9716_escuela-basica-acapulco_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9716_escuela-basica-acapulco_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3FB0BBF-86F4-4AA6-8A0E-222AADCAE032}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{231CFED2-0198-4637-9764-8095DE3C9BAC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{811E136B-FCD2-4F5B-B610-FD057659EEB3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{363D3813-9991-4592-BFDE-B25293060729}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3C363A4-B882-45E2-894A-BDA2BB70B165}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{86101712-7693-4828-801D-F51CA09F2C54}"/>
 </file>